--- a/data/codebook/Q14.xlsx
+++ b/data/codebook/Q14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PT-BR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN-US" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -563,7 +563,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -595,7 +595,7 @@
       <c r="Z1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Q14: For those characteristics that you considered to be a priority, please describe the reason for your classification. (Optional)</t>
         </is>
@@ -655,32 +655,32 @@
       <c r="Z3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Sub categoria</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Resposta</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -723,7 +723,7 @@
           <t xml:space="preserve"> These are the characteristics that I see as essential for reproducing techniques, whether for research or market purposes.</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>These are the characteristics that I see as essential for reproducing techniques, whether for research or market purposes. Ensuring these characteristics also influences faster development.</t>
         </is>
@@ -771,7 +771,7 @@
           <t>Reliability is key to ensuring that the data truly reflects the area of ​​knowledge being targeted.</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>Reliability is key to ensuring that the data truly reflects the area of ​​knowledge being targeted.</t>
         </is>
@@ -819,7 +819,7 @@
           <t>several scenarios where all of these words are extremely essential as well. But it will depend too much on the project in question</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>I can imagine several scenarios where all of these words are extremely essential as well. But it will depend too much on the project in question, so I prefer to use Neutral.</t>
         </is>
@@ -867,7 +867,7 @@
           <t xml:space="preserve"> will depend on the degree of error in the data and how precise the AM solution needs to be. But in general, having a certain level of precision is essential for any context</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>All requirements are essential depending on the context.
 Precision, for example, will depend on the degree of error in the data and how precise the AM solution needs to be. But in general, having a certain level of precision is essential for any context.
@@ -919,7 +919,7 @@
           <t>depends on how sensitive the data is. In hospital or banking data, for example, this aspect is super important</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>All requirements are essential depending on the context.
 Precision, for example, will depend on the degree of error in the data and how precise the AM solution needs to be. But in general, having a certain level of precision is essential for any context.
@@ -971,7 +971,7 @@
           <t>will depend on whether the system is used in real time or not.</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>All requirements are essential depending on the context.
 Precision, for example, will depend on the degree of error in the data and how precise the AM solution needs to be. But in general, having a certain level of precision is essential for any context.
@@ -1023,7 +1023,7 @@
           <t>These are priority criteria, but they do not impact functional requirements.</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>These are priority criteria, but they do not impact functional requirements.</t>
         </is>
@@ -1071,7 +1071,7 @@
           <t>will indicate how accurately the data actually represent real-world scenarios</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Consistency and completeness will indicate how accurately the data actually represent real-world scenarios; the model will tend to be more accurate if these aspects are prioritized.</t>
         </is>
@@ -1119,7 +1119,7 @@
           <t xml:space="preserve"> can lead to models that may have overfitting or underfitting problems</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Points marked as priorities, if not considered at the beginning of the project, can lead to models that may have overfitting or underfitting problems. This can be corrected by the team, but it is something that can be prevented with data that already has credibility, precision, and consistency, for example.</t>
         </is>
@@ -1167,7 +1167,7 @@
           <t xml:space="preserve"> otherwise, all results will be dubious and unreliable</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Same reason. All data used in the execution of ML algorithms must be of good quality; otherwise, all results will be dubious and unreliable. There is no middle ground.</t>
         </is>
@@ -1215,7 +1215,7 @@
           <t>To make decisions based on this data, the information must be accurate and consistent</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>I believe that data must be reliable and meaningful, as this is fundamental for the system to function correctly when put into production. To make decisions based on this data, the information must be accurate and consistent.</t>
         </is>
@@ -1263,7 +1263,7 @@
           <t>that data must be reliable and meaningful, as this is fundamental for the system to function correctly when put into production</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>I believe that data must be reliable and meaningful, as this is fundamental for the system to function correctly when put into production. To make decisions based on this data, the information must be accurate and consistent.</t>
         </is>
@@ -1311,7 +1311,7 @@
           <t>The more consistent the data, the better the ranking.</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>The more consistent the data, the better the ranking.</t>
         </is>
